--- a/data/trans_orig/IQ2601_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ2601_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47568</t>
+          <t>47583</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62464</t>
+          <t>61941</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59210</t>
+          <t>59821</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74793</t>
+          <t>75267</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111107</t>
+          <t>111895</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132473</t>
+          <t>132730</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,65%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9179</t>
+          <t>9129</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20681</t>
+          <t>20632</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19885</t>
+          <t>19113</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20573</t>
+          <t>19773</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35562</t>
+          <t>35169</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15583</t>
+          <t>16277</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>7667</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18757</t>
+          <t>18108</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15601</t>
+          <t>16125</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30018</t>
+          <t>30061</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3431</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17341</t>
+          <t>17070</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7573</t>
+          <t>7575</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17509</t>
+          <t>18169</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16356</t>
+          <t>17229</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31450</t>
+          <t>31561</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111784</t>
+          <t>109705</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>136293</t>
+          <t>137309</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>113794</t>
+          <t>114878</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>139867</t>
+          <t>140082</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>233529</t>
+          <t>233277</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>269238</t>
+          <t>268903</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,09%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52597</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74100</t>
+          <t>75632</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52229</t>
+          <t>51312</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73803</t>
+          <t>74069</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111591</t>
+          <t>111109</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143367</t>
+          <t>142548</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,14%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40652</t>
+          <t>41608</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61200</t>
+          <t>61190</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40578</t>
+          <t>39891</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61137</t>
+          <t>60751</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>86413</t>
+          <t>88245</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115234</t>
+          <t>116355</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>2917</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10432</t>
+          <t>10847</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4237</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13518</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16703</t>
+          <t>15149</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18886</t>
+          <t>19025</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15198</t>
+          <t>15302</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30265</t>
+          <t>29857</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43897</t>
+          <t>43573</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61034</t>
+          <t>61506</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53293</t>
+          <t>53718</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72158</t>
+          <t>72869</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102067</t>
+          <t>103000</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>128020</t>
+          <t>128960</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,93%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27020</t>
+          <t>27130</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43518</t>
+          <t>44168</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24553</t>
+          <t>24118</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40980</t>
+          <t>39986</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55484</t>
+          <t>55641</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78891</t>
+          <t>77942</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,97%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26026</t>
+          <t>26128</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41666</t>
+          <t>42146</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22923</t>
+          <t>23139</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38974</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>54309</t>
+          <t>52908</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75171</t>
+          <t>75758</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,16%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>633</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6124</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16222</t>
+          <t>15435</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6953</t>
+          <t>7194</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>18415</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9260</t>
+          <t>8782</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11622</t>
+          <t>11626</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6839</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18025</t>
+          <t>18092</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41978</t>
+          <t>41405</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>62061</t>
+          <t>61350</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48582</t>
+          <t>50037</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69915</t>
+          <t>70519</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>97499</t>
+          <t>96818</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>125389</t>
+          <t>125505</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>46533</t>
+          <t>46464</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>67198</t>
+          <t>66896</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>29982</t>
+          <t>30816</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47865</t>
+          <t>48702</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>82021</t>
+          <t>83298</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>110204</t>
+          <t>111129</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41747</t>
+          <t>42488</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>61622</t>
+          <t>62626</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>50910</t>
+          <t>49536</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>71929</t>
+          <t>71310</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>97446</t>
+          <t>98141</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>125562</t>
+          <t>126703</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10540</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22938</t>
+          <t>23049</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11627</t>
+          <t>10777</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24417</t>
+          <t>24241</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>24538</t>
+          <t>24158</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>43340</t>
+          <t>41577</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12538</t>
+          <t>13070</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25886</t>
+          <t>25277</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>24101</t>
+          <t>23966</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>39688</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>40696</t>
+          <t>39705</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>61292</t>
+          <t>61712</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>261211</t>
+          <t>263129</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>302808</t>
+          <t>303026</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>296275</t>
+          <t>293491</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>338652</t>
+          <t>336796</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>569715</t>
+          <t>570991</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>624687</t>
+          <t>627977</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>151083</t>
+          <t>150806</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>187087</t>
+          <t>186388</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>129510</t>
+          <t>129697</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>163261</t>
+          <t>163974</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>289172</t>
+          <t>289825</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>338419</t>
+          <t>339162</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>130364</t>
+          <t>130200</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>165276</t>
+          <t>163718</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>136134</t>
+          <t>137187</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>172021</t>
+          <t>172529</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>273433</t>
+          <t>276220</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>324518</t>
+          <t>324213</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>17118</t>
+          <t>16961</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>32421</t>
+          <t>32215</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>21465</t>
+          <t>21562</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>37893</t>
+          <t>37823</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>42347</t>
+          <t>42089</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>65254</t>
+          <t>64959</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>33642</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>53420</t>
+          <t>54928</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>51320</t>
+          <t>50548</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>75672</t>
+          <t>74767</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>91076</t>
+          <t>90055</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>122565</t>
+          <t>123160</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36784</t>
+          <t>37074</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55685</t>
+          <t>54187</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32482</t>
+          <t>32698</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50109</t>
+          <t>50252</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74312</t>
+          <t>74944</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98752</t>
+          <t>98814</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,66%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>10222</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21408</t>
+          <t>21489</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17523</t>
+          <t>17800</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31664</t>
+          <t>32179</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30547</t>
+          <t>30893</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49253</t>
+          <t>49540</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17671</t>
+          <t>17949</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32525</t>
+          <t>32339</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12530</t>
+          <t>12963</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26077</t>
+          <t>26452</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34112</t>
+          <t>34735</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53863</t>
+          <t>53925</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>11307</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12966</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>8626</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19835</t>
+          <t>20133</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26346</t>
+          <t>26166</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41914</t>
+          <t>42182</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19955</t>
+          <t>20034</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36440</t>
+          <t>34756</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>50092</t>
+          <t>51350</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71509</t>
+          <t>72343</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,76%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71307</t>
+          <t>70931</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94935</t>
+          <t>95673</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79101</t>
+          <t>77319</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104300</t>
+          <t>105200</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>155779</t>
+          <t>154654</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>191604</t>
+          <t>190996</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,86%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46523</t>
+          <t>48297</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68196</t>
+          <t>69442</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49210</t>
+          <t>48526</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71774</t>
+          <t>71816</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103470</t>
+          <t>101990</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>134133</t>
+          <t>133836</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,53%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32068</t>
+          <t>30906</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52007</t>
+          <t>49712</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44857</t>
+          <t>44433</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67419</t>
+          <t>66573</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>81847</t>
+          <t>81728</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>109846</t>
+          <t>110823</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3338</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12128</t>
+          <t>12014</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,47 +5411,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>5,1%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>13849</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8237</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>21562</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>5,15%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>13849</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>8084</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>21783</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,15%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14147</t>
+          <t>13982</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31260</t>
+          <t>29762</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37850</t>
+          <t>38753</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58518</t>
+          <t>59696</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40326</t>
+          <t>40482</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60314</t>
+          <t>61412</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>82303</t>
+          <t>84440</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>112000</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34230</t>
+          <t>34638</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53107</t>
+          <t>53174</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39053</t>
+          <t>40149</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57840</t>
+          <t>58883</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>78309</t>
+          <t>79178</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>104395</t>
+          <t>106105</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,68%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24636</t>
+          <t>24819</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41182</t>
+          <t>41239</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25808</t>
+          <t>25766</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42927</t>
+          <t>42413</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55024</t>
+          <t>53993</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78693</t>
+          <t>79058</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28924</t>
+          <t>28585</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45985</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23239</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40368</t>
+          <t>39418</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>56246</t>
+          <t>55642</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>80503</t>
+          <t>80234</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,47%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6987</t>
+          <t>6559</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19162</t>
+          <t>18386</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8867</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21188</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18465</t>
+          <t>18638</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34819</t>
+          <t>35523</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24743</t>
+          <t>24329</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41441</t>
+          <t>41446</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22617</t>
+          <t>23033</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39561</t>
+          <t>39395</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>52490</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>75079</t>
+          <t>75297</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,9%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38159</t>
+          <t>38103</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57566</t>
+          <t>57653</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20820</t>
+          <t>21466</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36648</t>
+          <t>37055</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63421</t>
+          <t>64223</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>89415</t>
+          <t>88689</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28482</t>
+          <t>28112</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47430</t>
+          <t>45335</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22512</t>
+          <t>23126</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38290</t>
+          <t>38478</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>54683</t>
+          <t>56399</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>78809</t>
+          <t>79897</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35152</t>
+          <t>33911</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>54237</t>
+          <t>54056</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>42130</t>
+          <t>42231</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>61613</t>
+          <t>60823</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>82369</t>
+          <t>81837</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>109487</t>
+          <t>109741</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,24%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20757</t>
+          <t>21386</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18222</t>
+          <t>18177</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33390</t>
+          <t>32092</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29850</t>
+          <t>30829</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>48910</t>
+          <t>49731</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20789</t>
+          <t>20828</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36786</t>
+          <t>37371</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>36345</t>
+          <t>36705</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>56172</t>
+          <t>54845</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>62596</t>
+          <t>62461</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>88548</t>
+          <t>86287</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>198018</t>
+          <t>198657</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>239767</t>
+          <t>238785</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>187924</t>
+          <t>186512</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>230646</t>
+          <t>226925</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>398060</t>
+          <t>399688</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>455568</t>
+          <t>456513</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>124126</t>
+          <t>125279</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>160064</t>
+          <t>158175</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>132036</t>
+          <t>130322</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>165449</t>
+          <t>165290</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>264106</t>
+          <t>266112</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>317496</t>
+          <t>316600</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>128697</t>
+          <t>128096</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>162517</t>
+          <t>163941</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>136866</t>
+          <t>137316</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>173432</t>
+          <t>175016</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>276533</t>
+          <t>278578</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>326542</t>
+          <t>329837</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>49345</t>
+          <t>49115</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>47633</t>
+          <t>47489</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>74126</t>
+          <t>72983</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>83914</t>
+          <t>83515</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>115181</t>
+          <t>116044</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>127810</t>
+          <t>125313</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>160980</t>
+          <t>161043</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>135972</t>
+          <t>135304</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>172286</t>
+          <t>172713</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>271298</t>
+          <t>271604</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>325784</t>
+          <t>320847</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28049</t>
+          <t>27797</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43355</t>
+          <t>44120</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32986</t>
+          <t>33751</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50501</t>
+          <t>49441</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66888</t>
+          <t>66610</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90688</t>
+          <t>90472</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,1%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>20448</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35796</t>
+          <t>35456</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21052</t>
+          <t>21132</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36124</t>
+          <t>35524</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45687</t>
+          <t>45995</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66824</t>
+          <t>67516</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13395</t>
+          <t>13953</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13924</t>
+          <t>13942</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11354</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23463</t>
+          <t>24784</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9396</t>
+          <t>9244</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10955</t>
+          <t>10591</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39762</t>
+          <t>40892</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56465</t>
+          <t>57903</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26253</t>
+          <t>26526</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41677</t>
+          <t>42152</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>69975</t>
+          <t>70128</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>93853</t>
+          <t>94119</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,63%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59767</t>
+          <t>60167</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82021</t>
+          <t>81556</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74245</t>
+          <t>73789</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97963</t>
+          <t>97698</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>141093</t>
+          <t>140339</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>171999</t>
+          <t>172001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57613</t>
+          <t>56685</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78097</t>
+          <t>77855</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71057</t>
+          <t>70349</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94307</t>
+          <t>93745</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133802</t>
+          <t>133719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>166001</t>
+          <t>165812</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,39%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12647</t>
+          <t>12715</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>26466</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21120</t>
+          <t>22207</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38012</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>37860</t>
+          <t>37585</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>59029</t>
+          <t>58728</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7222</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18633</t>
+          <t>18389</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16004</t>
+          <t>17245</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15242</t>
+          <t>14743</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31059</t>
+          <t>30443</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34148</t>
+          <t>33039</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53502</t>
+          <t>51788</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>41995</t>
+          <t>42519</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62683</t>
+          <t>61562</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>79655</t>
+          <t>80522</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>107760</t>
+          <t>106854</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,8%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52237</t>
+          <t>51553</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73944</t>
+          <t>72709</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50192</t>
+          <t>49621</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71803</t>
+          <t>71577</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108207</t>
+          <t>107488</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>137591</t>
+          <t>137027</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,3%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56339</t>
+          <t>55314</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78331</t>
+          <t>78124</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>56149</t>
+          <t>54238</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>77358</t>
+          <t>76289</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>118518</t>
+          <t>119809</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>148288</t>
+          <t>150242</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,8%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10869</t>
+          <t>10167</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23859</t>
+          <t>23214</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21318</t>
+          <t>20917</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37437</t>
+          <t>37634</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>34609</t>
+          <t>35663</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>55292</t>
+          <t>56911</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11198</t>
+          <t>11377</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>8532</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>5825</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>16451</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29575</t>
+          <t>29592</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48178</t>
+          <t>47852</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22232</t>
+          <t>22413</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40232</t>
+          <t>39627</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>56414</t>
+          <t>55451</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>80365</t>
+          <t>82333</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41240</t>
+          <t>41232</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61843</t>
+          <t>61114</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33383</t>
+          <t>34133</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52386</t>
+          <t>52528</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80671</t>
+          <t>80765</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108092</t>
+          <t>108151</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,14%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>53917</t>
+          <t>53340</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>74827</t>
+          <t>74618</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>57115</t>
+          <t>56967</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>78892</t>
+          <t>78154</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>116656</t>
+          <t>117103</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>147766</t>
+          <t>146330</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,13%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16596</t>
+          <t>15611</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31228</t>
+          <t>31509</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14362</t>
+          <t>14356</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27909</t>
+          <t>28593</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33085</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>54395</t>
+          <t>53791</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9888</t>
+          <t>9735</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15509</t>
+          <t>15323</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>8456</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22141</t>
+          <t>21731</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22806</t>
+          <t>22901</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>39815</t>
+          <t>41162</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>26086</t>
+          <t>25800</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>42774</t>
+          <t>43386</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>53692</t>
+          <t>54544</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>79025</t>
+          <t>78189</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>197221</t>
+          <t>198697</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>236994</t>
+          <t>236519</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>208469</t>
+          <t>209137</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>250688</t>
+          <t>251510</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>420693</t>
+          <t>420442</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>476349</t>
+          <t>476569</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,31%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>206087</t>
+          <t>207022</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>247265</t>
+          <t>247665</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>223911</t>
+          <t>224556</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>267559</t>
+          <t>268805</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>441092</t>
+          <t>443165</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>498702</t>
+          <t>502193</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>53445</t>
+          <t>53748</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>78077</t>
+          <t>78897</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>72732</t>
+          <t>72783</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>102770</t>
+          <t>101918</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>134649</t>
+          <t>134000</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>171386</t>
+          <t>171541</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>17015</t>
+          <t>17200</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>32771</t>
+          <t>33760</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>19884</t>
+          <t>19602</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>37424</t>
+          <t>37389</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>40291</t>
+          <t>40627</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>64828</t>
+          <t>64682</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>142822</t>
+          <t>142533</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>178275</t>
+          <t>178356</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>131632</t>
+          <t>131401</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>166683</t>
+          <t>166543</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>282618</t>
+          <t>282595</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>334049</t>
+          <t>333341</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3907</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>9096</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9419</t>
+          <t>9282</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9498</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17196</t>
+          <t>17098</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>61,84%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6150</t>
+          <t>5719</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2411</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7953</t>
+          <t>7858</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4797</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12369</t>
+          <t>11920</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>43,12%</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5547</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>611</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>753</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7126</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17225</t>
+          <t>16544</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>6720</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16894</t>
+          <t>16674</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15855</t>
+          <t>15767</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30961</t>
+          <t>30154</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,12%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10187</t>
+          <t>9718</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18930</t>
+          <t>18938</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14002</t>
+          <t>13504</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24516</t>
+          <t>24799</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27004</t>
+          <t>26920</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41886</t>
+          <t>40871</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>51,67%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>420</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10021</t>
+          <t>9966</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12541</t>
+          <t>11692</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5465</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12720,7 +12720,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12735,7 +12735,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7098</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12427</t>
+          <t>12891</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>7913</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19022</t>
+          <t>18483</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>3693</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12374</t>
+          <t>12564</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11386</t>
+          <t>10973</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26318</t>
+          <t>25064</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17830</t>
+          <t>17385</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34485</t>
+          <t>34274</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>15654</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27711</t>
+          <t>27971</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17678</t>
+          <t>18010</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31955</t>
+          <t>31841</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36664</t>
+          <t>36646</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55630</t>
+          <t>56730</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>59,14%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2333</t>
+          <t>2556</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>9712</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>12250</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>6893</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18764</t>
+          <t>18231</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>2417</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>9397</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>758</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13168</t>
+          <t>13112</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11538</t>
+          <t>11579</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22444</t>
+          <t>22740</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9607</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22465</t>
+          <t>22308</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23970</t>
+          <t>23836</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41395</t>
+          <t>40884</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13096</t>
+          <t>12851</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24409</t>
+          <t>23756</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31621</t>
+          <t>32931</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49765</t>
+          <t>50473</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>47908</t>
+          <t>49292</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>70786</t>
+          <t>72011</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,91%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16973</t>
+          <t>16708</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18057</t>
+          <t>17501</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14320</t>
+          <t>14709</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29856</t>
+          <t>29366</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>518</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1431</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8972</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11973</t>
+          <t>11453</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15968</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>8734</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23171</t>
+          <t>23521</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>32918</t>
+          <t>33317</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51454</t>
+          <t>52833</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>39453</t>
+          <t>40833</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>61544</t>
+          <t>63218</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>78612</t>
+          <t>78981</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>107942</t>
+          <t>107965</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>47933</t>
+          <t>47381</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>67901</t>
+          <t>67057</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>76884</t>
+          <t>76211</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>104283</t>
+          <t>103316</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>130084</t>
+          <t>130279</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>164376</t>
+          <t>164177</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,18%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13515</t>
+          <t>13279</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26508</t>
+          <t>26296</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17758</t>
+          <t>17829</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>34728</t>
+          <t>33891</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>34186</t>
+          <t>34000</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>55141</t>
+          <t>55992</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12109</t>
+          <t>12044</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12992</t>
+          <t>13595</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8675</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>21994</t>
+          <t>22411</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11163</t>
+          <t>10979</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>24741</t>
+          <t>24588</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>12543</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>29054</t>
+          <t>28293</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>26994</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>47091</t>
+          <t>48316</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
